--- a/mappingCorps/ig/StructureDefinition-fr-lm-multidrug-resistant-microorganism-identification.xlsx
+++ b/mappingCorps/ig/StructureDefinition-fr-lm-multidrug-resistant-microorganism-identification.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -448,13 +448,13 @@
     <t>fr-lm-entry.header.language</t>
   </si>
   <si>
-    <t>fr-lm-multidrug-resistant-microorganism-identification.code</t>
+    <t>fr-lm-multidrug-resistant-microorganism-identification.type</t>
   </si>
   <si>
     <t>Code de l’observation</t>
   </si>
   <si>
-    <t>fr-lm-multidrug-resistant-microorganism-identification.value</t>
+    <t>fr-lm-multidrug-resistant-microorganism-identification.result</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -797,7 +797,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="48.296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="48.484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
